--- a/data/export/2026-09-17-operations.xlsx
+++ b/data/export/2026-09-17-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -648,29 +648,29 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -772,29 +772,29 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -896,29 +896,29 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车08:15，减去该车自身同类时段历史终点停站中位数23分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1273,24 +1273,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±10分钟</t>
+          <t>07:11采样：该车到重点站唐陆公路顾家浜路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1607,24 +1607,24 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1637,34 +1637,34 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1713,40 +1713,40 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1761,24 +1761,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1837,40 +1837,40 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站沪南路高科西路 ETA 42分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±14分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±13分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1961,40 +1961,40 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2009,22 +2009,26 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2032,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2046,7 +2050,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2056,61 +2060,65 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2125,30 +2133,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2162,7 +2174,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2172,17 +2184,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2192,41 +2204,45 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2241,30 +2257,34 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2278,7 +2298,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2288,17 +2308,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2308,41 +2328,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2357,30 +2381,34 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2394,7 +2422,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2404,61 +2432,65 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2473,24 +2505,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数171分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2500,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2514,7 +2546,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2539,22 +2571,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2567,24 +2599,24 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2597,19 +2629,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数161分钟估算，约±5分钟</t>
+          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2619,12 +2651,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2638,7 +2670,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2653,7 +2685,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2673,30 +2705,30 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2706,7 +2738,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2721,30 +2753,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 76分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>07:19采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2768,17 +2804,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2788,41 +2824,45 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2837,34 +2877,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
+          <t>07:19采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2878,7 +2918,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2888,12 +2928,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2913,40 +2953,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2961,34 +3001,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数109分钟估算，约±15分钟</t>
+          <t>07:19采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3002,7 +3042,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3012,12 +3052,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3037,40 +3077,40 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3103,12 +3143,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3122,7 +3162,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3158,7 +3198,3551 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康沈路秀康路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数145分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>176分钟</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康沈路秀康路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>176.0</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>179分钟</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数174分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>153分钟</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数153分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>175分钟</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数175分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:18采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>07:18采样：该车到重点站五莲路东陆路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站花山路杨高北路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数101分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-operations.xlsx
+++ b/data/export/2026-09-17-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,14 +447,14 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -777,24 +777,24 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1020,29 +1020,29 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车08:15，减去该车自身同类时段历史终点停站中位数23分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1149,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1268,29 +1268,29 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>07:11采样：该车到重点站唐陆公路顾家浜路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1392,27 +1392,31 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1420,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1508,29 +1516,29 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±12分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1540,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1564,12 +1572,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1579,22 +1587,22 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1637,26 +1645,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1664,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1693,7 +1697,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1703,22 +1707,22 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1756,29 +1760,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1812,12 +1816,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1827,22 +1831,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1885,24 +1889,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±13分钟</t>
+          <t>08:21采样：该车到重点站博兴路东陆路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1912,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1936,12 +1940,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1961,12 +1965,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2009,26 +2013,22 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 46分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2133,24 +2133,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2257,19 +2257,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2475,24 +2475,24 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2505,24 +2505,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2581,40 +2581,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2629,19 +2629,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦建路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 29分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2695,50 +2695,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2753,24 +2753,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±15分钟</t>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2819,50 +2819,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2877,34 +2877,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±15分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2928,12 +2928,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2953,40 +2953,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3001,34 +3001,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±14分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3067,50 +3067,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3125,22 +3125,26 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3162,7 +3166,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3172,61 +3176,65 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3241,22 +3249,26 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -3264,7 +3276,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3278,7 +3290,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3288,61 +3300,65 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3357,19 +3373,19 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3379,12 +3395,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3398,7 +3414,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3413,7 +3429,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3423,50 +3439,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3481,34 +3497,34 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康沈路秀康路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3522,7 +3538,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3537,7 +3553,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3547,22 +3563,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3591,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3585,7 +3601,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3600,39 +3616,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3646,7 +3662,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3656,12 +3672,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3671,22 +3687,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3699,24 +3715,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3724,39 +3740,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数145分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3770,7 +3786,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3780,12 +3796,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3795,22 +3811,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3823,24 +3839,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3848,39 +3864,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康沈路秀康路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3894,7 +3910,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3904,12 +3920,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3929,12 +3945,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3963,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3957,7 +3973,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3977,30 +3993,34 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站长岛路张杨北路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4014,7 +4034,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4024,33 +4044,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4087,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4073,7 +4097,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4083,44 +4107,40 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4128,13 +4148,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4144,17 +4180,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4164,17 +4200,13 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4187,24 +4219,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4217,34 +4249,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>179分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>07:19采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数174分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4258,7 +4286,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4268,17 +4296,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4288,17 +4316,13 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>179.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4335,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4321,7 +4345,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4341,30 +4365,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4378,7 +4406,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4388,17 +4416,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4408,13 +4436,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4427,24 +4459,24 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4457,34 +4489,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数153分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4498,7 +4530,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4513,7 +4545,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4533,12 +4565,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4551,24 +4583,24 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4581,34 +4613,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数175分钟估算，约±12分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4622,7 +4654,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4632,12 +4664,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4657,12 +4689,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4707,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4685,7 +4717,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4705,19 +4737,19 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4732,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4746,7 +4778,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4761,7 +4793,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4781,40 +4813,40 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4829,30 +4861,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:18采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站沪南路高科西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4866,7 +4902,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4881,7 +4917,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4891,50 +4927,50 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4949,34 +4985,30 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4990,7 +5022,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5000,17 +5032,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5020,45 +5052,41 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5073,34 +5101,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>07:18采样：该车到重点站五莲路东陆路 ETA 27分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5114,7 +5142,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5149,40 +5177,40 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5197,30 +5225,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站锦绣路花木路 ETA 35分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5234,7 +5266,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5244,17 +5276,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5264,41 +5296,45 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5313,34 +5349,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5354,7 +5386,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5364,17 +5396,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5384,45 +5416,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5437,30 +5465,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5474,7 +5506,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5484,17 +5516,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5504,41 +5536,45 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5553,34 +5589,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>185分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站花山路杨高北路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5594,7 +5630,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5604,7 +5640,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5629,40 +5665,40 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5677,34 +5713,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>07:10采样：该车到重点站张杨北路博兴路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5718,7 +5754,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5753,40 +5789,40 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5801,19 +5837,19 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数150分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5823,12 +5859,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5842,7 +5878,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5857,7 +5893,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5877,40 +5913,40 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5925,30 +5961,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5962,7 +6002,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5972,17 +6012,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5992,41 +6032,45 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6041,19 +6085,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>08:10采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6063,12 +6107,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6082,7 +6126,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6097,7 +6141,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -6117,40 +6161,40 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6165,34 +6209,34 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+          <t>08:20采样：该车到重点站博兴路兰城路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6206,7 +6250,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6221,7 +6265,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6241,40 +6285,40 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6289,34 +6333,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数101分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6330,7 +6374,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6345,7 +6389,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6365,40 +6409,40 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6413,34 +6457,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+          <t>08:20采样：该车到重点站川周公路康沈路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6454,7 +6498,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6469,7 +6513,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6489,40 +6533,40 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6537,34 +6581,30 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6578,7 +6618,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6588,17 +6628,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6608,45 +6648,41 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6661,19 +6697,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6683,12 +6719,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6702,47 +6738,3731 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>115分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>07:50采样：该车到重点站五莲路凌河路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 35分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>07:50采样：该车到重点站金高路行泰路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金高路万安街 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金高路源华路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="AD51" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-operations.xlsx
+++ b/data/export/2026-09-17-operations.xlsx
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10761,12 +10761,12 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11668,27 +11668,31 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11696,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11720,12 +11724,12 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11745,7 +11749,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11788,29 +11792,29 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -11820,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11844,12 +11848,12 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11869,12 +11873,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11912,29 +11916,29 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -11944,7 +11948,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11968,12 +11972,12 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11993,7 +11997,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12036,24 +12040,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -12068,7 +12072,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12092,12 +12096,12 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -12117,12 +12121,12 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12165,26 +12169,22 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12216,12 +12216,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12289,19 +12289,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>21:21采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12613,12 +12613,12 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13733,12 +13733,12 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14497,12 +14497,12 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14861,12 +14861,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15472,17 +15472,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16217,12 +16217,12 @@
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16841,12 +16841,12 @@
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17213,12 +17213,12 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17586,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18077,12 +18077,12 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18568,17 +18568,17 @@
       </c>
       <c r="AB146" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC146" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19764,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -21128,7 +21128,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21177,12 +21177,12 @@
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -21756,7 +21756,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
@@ -21880,7 +21880,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21929,12 +21929,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -22000,7 +22000,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -22244,7 +22244,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22293,12 +22293,12 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22417,12 +22417,12 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22536,17 +22536,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -22612,7 +22612,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22736,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -22914,7 +22914,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -22980,7 +22980,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23029,12 +23029,12 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -23158,7 +23158,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23401,12 +23401,12 @@
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -23530,7 +23530,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -23778,7 +23778,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -23950,17 +23950,21 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23968,7 +23972,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23992,12 +23996,12 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
@@ -24017,12 +24021,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -24212,7 +24216,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24261,7 +24265,7 @@
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
@@ -24304,29 +24308,29 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站东波路莱阳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O193" s="2" t="inlineStr">
@@ -24336,7 +24340,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24360,12 +24364,12 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
@@ -24385,12 +24389,12 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -24428,27 +24432,31 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -24456,7 +24464,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24480,17 +24488,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24500,13 +24508,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC194" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC194" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -24544,29 +24556,29 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O195" s="2" t="inlineStr">
@@ -24576,7 +24588,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24600,12 +24612,12 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
@@ -24625,12 +24637,12 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -24787,36 +24799,32 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>20:10采样：该车到重点站丁香路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -24824,18 +24832,30 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="Q197" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="R197" s="2" t="inlineStr"/>
-      <c r="S197" s="2" t="inlineStr"/>
       <c r="T197" s="2" t="inlineStr"/>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V197" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24848,17 +24868,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24868,17 +24888,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -24916,29 +24936,29 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
@@ -24948,7 +24968,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24972,12 +24992,12 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
@@ -24997,12 +25017,12 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -25040,24 +25060,24 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
@@ -25072,7 +25092,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25096,12 +25116,12 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
@@ -25121,7 +25141,7 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.6</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
@@ -25192,7 +25212,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25246,7 +25266,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -25279,12 +25299,12 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -25312,7 +25332,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25320,10 +25340,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R201" s="2" t="inlineStr"/>
-      <c r="S201" s="2" t="inlineStr"/>
-      <c r="T201" s="2" t="inlineStr"/>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V201" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -25341,7 +25377,7 @@
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
@@ -25366,7 +25402,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -25432,7 +25468,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25486,7 +25522,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -25524,29 +25560,29 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O203" s="2" t="inlineStr">
@@ -25556,7 +25592,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25580,12 +25616,12 @@
       </c>
       <c r="X203" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y203" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z203" s="2" t="inlineStr">
@@ -25605,12 +25641,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -25653,19 +25689,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
@@ -25680,7 +25716,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25729,7 +25765,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25777,24 +25813,24 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±9分钟</t>
+          <t>21:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -25804,7 +25840,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25853,12 +25889,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -25906,19 +25942,19 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>21:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O206" s="2" t="inlineStr">
@@ -25928,7 +25964,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25952,12 +25988,12 @@
       </c>
       <c r="X206" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y206" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z206" s="2" t="inlineStr">
@@ -25977,12 +26013,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -26025,24 +26061,24 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O207" s="2" t="inlineStr">
@@ -26052,7 +26088,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26081,7 +26117,7 @@
       </c>
       <c r="Y207" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z207" s="2" t="inlineStr">
@@ -26101,7 +26137,7 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>128.8</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26172,7 +26208,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26221,12 +26257,12 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26346,7 +26382,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -26466,7 +26502,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26696,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26709,12 +26745,12 @@
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -26780,7 +26816,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26829,12 +26865,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27082,7 +27118,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27152,7 +27188,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27201,7 +27237,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27276,7 +27312,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27320,17 +27356,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -27698,7 +27734,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28012,7 +28048,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28061,12 +28097,12 @@
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28136,7 +28172,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28185,12 +28221,12 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28562,7 +28598,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -28752,7 +28788,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28801,12 +28837,12 @@
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -28930,7 +28966,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29090,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29160,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29173,12 +29209,12 @@
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29372,7 +29408,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29416,17 +29452,17 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29532,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29545,7 +29581,7 @@
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
@@ -29922,7 +29958,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -30116,7 +30152,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30165,12 +30201,12 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30294,7 +30330,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -30484,7 +30520,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30545,12 +30581,12 @@
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -30674,7 +30710,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30798,7 +30834,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30900,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30920,17 +30956,17 @@
       </c>
       <c r="AB246" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -31550,7 +31586,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31710,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -31922,7 +31958,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32082,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32666,7 +32702,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32826,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33074,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33108,7 +33144,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33157,12 +33193,12 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33286,7 +33322,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33852,7 +33888,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33901,12 +33937,12 @@
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33976,7 +34012,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -34025,7 +34061,7 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
@@ -34402,7 +34438,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34472,7 +34508,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34521,12 +34557,12 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -34596,7 +34632,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34645,12 +34681,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34810,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -34844,7 +34880,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34888,17 +34924,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35146,7 +35182,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35270,7 +35306,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35340,7 +35376,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35389,12 +35425,12 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36120,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36133,12 +36169,12 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36208,7 +36244,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36257,7 +36293,7 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36510,7 +36546,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36580,7 +36616,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36629,12 +36665,12 @@
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -36704,7 +36740,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36753,12 +36789,12 @@
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37006,7 +37042,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -37076,7 +37112,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37120,17 +37156,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37250,7 +37286,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37374,7 +37410,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37560,7 +37596,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37609,12 +37645,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38048,7 +38084,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38097,12 +38133,12 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38145,24 +38181,24 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N305" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O305" s="2" t="inlineStr">
@@ -38172,7 +38208,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38221,12 +38257,12 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -38264,27 +38300,31 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38292,7 +38332,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38316,12 +38356,12 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
@@ -38341,7 +38381,7 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
@@ -38384,27 +38424,31 @@
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 59分钟</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O307" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38412,7 +38456,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38436,17 +38480,17 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA307" s="2" t="inlineStr">
@@ -38456,17 +38500,17 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -38504,29 +38548,29 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr"/>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N308" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O308" s="2" t="inlineStr">
@@ -38536,7 +38580,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38560,12 +38604,12 @@
       </c>
       <c r="X308" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr">
@@ -38585,12 +38629,12 @@
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -38633,26 +38677,22 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr"/>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站张杨北路金桥路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N309" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 14分钟</t>
+        </is>
+      </c>
+      <c r="N309" s="2" t="inlineStr"/>
       <c r="O309" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -38660,7 +38700,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38689,7 +38729,7 @@
       </c>
       <c r="Y309" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z309" s="2" t="inlineStr">
@@ -38709,12 +38749,12 @@
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38757,26 +38797,22 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr"/>
       <c r="L310" s="2" t="inlineStr"/>
       <c r="M310" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N310" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="N310" s="2" t="inlineStr"/>
       <c r="O310" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38784,7 +38820,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q310" s="2" t="inlineStr">
@@ -38808,12 +38844,12 @@
       </c>
       <c r="X310" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y310" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z310" s="2" t="inlineStr">
@@ -38833,12 +38869,12 @@
       </c>
       <c r="AC310" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD310" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38881,24 +38917,24 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr"/>
       <c r="M311" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±14分钟</t>
         </is>
       </c>
       <c r="N311" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O311" s="2" t="inlineStr">
@@ -38908,7 +38944,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q311" s="2" t="inlineStr">
@@ -38932,12 +38968,12 @@
       </c>
       <c r="X311" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y311" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z311" s="2" t="inlineStr">
@@ -38957,7 +38993,7 @@
       </c>
       <c r="AC311" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AD311" s="2" t="inlineStr">
@@ -39032,7 +39068,7 @@
       </c>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q312" s="2" t="inlineStr">
@@ -39081,12 +39117,12 @@
       </c>
       <c r="AC312" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AD312" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-17-operations.xlsx
+++ b/data/export/2026-09-17-operations.xlsx
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -12174,17 +12174,21 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 24分钟</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12192,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12216,12 +12220,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12241,7 +12245,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12284,29 +12288,29 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12316,7 +12320,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12340,12 +12344,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12365,7 +12369,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12413,26 +12417,22 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:21</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站长岛路台儿庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13684,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14492,17 +14492,17 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14861,12 +14861,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17700,17 +17700,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18077,12 +18077,12 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18826,7 +18826,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -22244,7 +22244,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22293,12 +22293,12 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -22980,7 +22980,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23396,17 +23396,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -24216,7 +24216,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24265,7 +24265,7 @@
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -24804,7 +24804,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25402,7 +25402,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25565,24 +25565,24 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O203" s="2" t="inlineStr">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25641,12 +25641,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -25684,7 +25684,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -25694,19 +25694,19 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路御桥路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O204" s="2" t="inlineStr">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25740,12 +25740,12 @@
       </c>
       <c r="X204" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y204" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z204" s="2" t="inlineStr">
@@ -25765,7 +25765,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25813,26 +25813,22 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N205" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr"/>
       <c r="O205" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -25840,7 +25836,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25869,7 +25865,7 @@
       </c>
       <c r="Y205" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z205" s="2" t="inlineStr">
@@ -25889,7 +25885,7 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
@@ -25937,26 +25933,22 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>22:39</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N206" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 54分钟</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr"/>
       <c r="O206" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -25964,7 +25956,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25988,17 +25980,17 @@
       </c>
       <c r="X206" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y206" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z206" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA206" s="2" t="inlineStr">
@@ -26008,17 +26000,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -26061,24 +26053,24 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±8分钟</t>
+          <t>21:51采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O207" s="2" t="inlineStr">
@@ -26088,7 +26080,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26137,7 +26129,7 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26208,7 +26200,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26257,12 +26249,12 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26502,7 +26494,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26816,7 +26808,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26865,12 +26857,12 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27118,7 +27110,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27188,7 +27180,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27237,12 +27229,12 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27734,7 +27726,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28048,7 +28040,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28097,12 +28089,12 @@
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28172,7 +28164,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28221,12 +28213,12 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28966,7 +28958,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29082,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29160,7 +29152,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29209,12 +29201,12 @@
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29532,7 +29524,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29581,12 +29573,12 @@
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29958,7 +29950,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30152,7 +30144,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30201,12 +30193,12 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30710,7 +30702,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30826,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31578,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31958,7 +31950,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32082,7 +32074,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32702,7 +32694,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33066,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33144,7 +33136,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33193,12 +33185,12 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33322,7 +33314,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -33888,7 +33880,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33937,12 +33929,12 @@
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34012,7 +34004,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -34061,12 +34053,12 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34438,7 +34430,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34632,7 +34624,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34681,12 +34673,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35182,7 +35174,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35306,7 +35298,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35376,7 +35368,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35425,12 +35417,12 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36120,7 +36112,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36169,12 +36161,12 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36236,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36293,12 +36285,12 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36546,7 +36538,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36740,7 +36732,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36789,12 +36781,12 @@
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37286,7 +37278,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -37410,7 +37402,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37596,7 +37588,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37645,12 +37637,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -38084,7 +38076,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38133,12 +38125,12 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38332,7 +38324,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38381,12 +38373,12 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -38580,7 +38572,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38629,12 +38621,12 @@
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -38672,27 +38664,31 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr"/>
       <c r="M309" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 14分钟</t>
-        </is>
-      </c>
-      <c r="N309" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O309" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -38700,7 +38696,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38724,12 +38720,12 @@
       </c>
       <c r="X309" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y309" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z309" s="2" t="inlineStr">
@@ -38749,12 +38745,12 @@
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -38792,27 +38788,31 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr"/>
       <c r="L310" s="2" t="inlineStr"/>
       <c r="M310" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 42分钟</t>
-        </is>
-      </c>
-      <c r="N310" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O310" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38820,7 +38820,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q310" s="2" t="inlineStr">
@@ -38844,12 +38844,12 @@
       </c>
       <c r="X310" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y310" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z310" s="2" t="inlineStr">
@@ -38869,12 +38869,12 @@
       </c>
       <c r="AC310" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD310" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38912,29 +38912,29 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr"/>
       <c r="M311" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N311" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O311" s="2" t="inlineStr">
@@ -38944,7 +38944,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q311" s="2" t="inlineStr">
@@ -38968,12 +38968,12 @@
       </c>
       <c r="X311" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y311" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z311" s="2" t="inlineStr">
@@ -38993,12 +38993,12 @@
       </c>
       <c r="AC311" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AD311" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -39046,14 +39046,14 @@
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr"/>
       <c r="L312" s="2" t="inlineStr"/>
       <c r="M312" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N312" s="2" t="inlineStr">
@@ -39068,7 +39068,7 @@
       </c>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q312" s="2" t="inlineStr">
@@ -39097,7 +39097,7 @@
       </c>
       <c r="Y312" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z312" s="2" t="inlineStr">
@@ -39117,12 +39117,12 @@
       </c>
       <c r="AC312" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD312" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
